--- a/menu.xlsx
+++ b/menu.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Miscellaneous\Mensa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\48233\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7B0081-8423-412E-B337-8DA532D543E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6760" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="menù inverno 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Menù celiaco inverno 2026" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="Excel_BuiltIn_Print_Area" localSheetId="1">#N/A</definedName>
     <definedName name="Excel_BuiltIn_Print_Area" localSheetId="0">#N/A</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="175">
   <si>
     <t>SETTIMANA 1</t>
   </si>
@@ -46,6 +47,9 @@
     <t>PASTA ALLA CARRETTIERA</t>
   </si>
   <si>
+    <t>PASTA ALLA TRAPANESE</t>
+  </si>
+  <si>
     <t>PASTA ALLA PUTTANESCA</t>
   </si>
   <si>
@@ -55,9 +59,18 @@
     <t>PASTA ALLE CIME DI RAPA</t>
   </si>
   <si>
+    <t>PASTA CON LE FAVE</t>
+  </si>
+  <si>
+    <t>PASTA ALLA FONDUTA FUME' CURCUMA E PEPE</t>
+  </si>
+  <si>
     <t>ZUPPA DI CANNELLINI</t>
   </si>
   <si>
+    <t>ZUPPA DI CECI</t>
+  </si>
+  <si>
     <t>MINESTRONE DI VERDURA</t>
   </si>
   <si>
@@ -67,18 +80,27 @@
     <t>FILETTO DI PERSICO AGLI AGRUMI</t>
   </si>
   <si>
+    <t>BOCCONCINI DI TACCHINO AL CURRY</t>
+  </si>
+  <si>
     <t>COSCIA DI POLLO ARROSTO</t>
   </si>
   <si>
     <t>WURSTELL E CRAUTI</t>
   </si>
   <si>
+    <t>COSCIA DI POLLO ALLA  PAPRIKA</t>
+  </si>
+  <si>
     <t>TORTA PASQUALINA</t>
   </si>
   <si>
     <t>SOFFICINO AL FORMAGGIO</t>
   </si>
   <si>
+    <t>FILETTO DI MERLUZZO ALLA MILANESE</t>
+  </si>
+  <si>
     <t>FILETTO DI MERLUZZO ALLE OLIVE</t>
   </si>
   <si>
@@ -94,115 +116,451 @@
     <t>MIX DI VERDURE</t>
   </si>
   <si>
+    <t xml:space="preserve">CAROTE </t>
+  </si>
+  <si>
     <t>MARTEDÌ</t>
   </si>
   <si>
+    <t>PASTA ALL' AMATRICIANA</t>
+  </si>
+  <si>
+    <t>RAVIOLI DI MAGRO AL BURRO E SALVIA</t>
+  </si>
+  <si>
     <t>RISOTTO ALLA MILANESE</t>
   </si>
   <si>
+    <t>RISOTTO AL RADICCHIO E VINO ROSSO</t>
+  </si>
+  <si>
+    <t>PASTA AL RADICCHIO  E GORGONZOLA</t>
+  </si>
+  <si>
     <t>PASTA AI CARCIOFI</t>
   </si>
   <si>
+    <t>PASTA AL POMODORO ROSMARINO E PATATE</t>
+  </si>
+  <si>
+    <t>PASTA AL POMODORO E COZZE</t>
+  </si>
+  <si>
+    <t>MINESTRA DI ZUCCHINE</t>
+  </si>
+  <si>
+    <t>ZUPPA DI PORRI</t>
+  </si>
+  <si>
     <t>ZUPPA DI ZUCCHINE</t>
   </si>
   <si>
+    <t>CASSEOUOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEBAB </t>
+  </si>
+  <si>
+    <t>CAPOCOLLO STUFATO AL VINO ROSSO</t>
+  </si>
+  <si>
+    <t>INSALATA DI TONNO,OLIVE E FAGIOLINI</t>
+  </si>
+  <si>
+    <t>FRITTATA CON CON VERDURE</t>
+  </si>
+  <si>
+    <t>FILETTO DI MERLUZZO IN MIREPOIX</t>
+  </si>
+  <si>
+    <t>BRASATO DI MANZO</t>
+  </si>
+  <si>
     <t>TORTINO DI PATATE GRATINATO</t>
   </si>
   <si>
     <t>FILETTO DI PERSICO ALLA CURCUMA</t>
   </si>
   <si>
+    <t>PROVOLONE CON POMODORO E ORIGANO</t>
+  </si>
+  <si>
+    <t>FILETTO DI PERSICO AL LIMONE</t>
+  </si>
+  <si>
+    <t>LENTICCHIE</t>
+  </si>
+  <si>
+    <t>FAGIOLI IN UMIDO</t>
+  </si>
+  <si>
+    <t>POLENTA</t>
+  </si>
+  <si>
     <t>MERCOLEDÌ</t>
   </si>
   <si>
+    <t>RISOTTO AL TALEGGIO</t>
+  </si>
+  <si>
+    <t>RISOTTO AI FUNGHI</t>
+  </si>
+  <si>
+    <t>PASTA ALL’ARRABBIATA</t>
+  </si>
+  <si>
+    <t>RAVIOLI  ALLA ZUCCA E SALSICCIA</t>
+  </si>
+  <si>
     <t>PASTA ALL'ARRABBIATA</t>
   </si>
   <si>
+    <t>PASTA AL TONNO E  CAPPERI</t>
+  </si>
+  <si>
+    <t>PASTA AI CAVOLINI DI BRUXELLES</t>
+  </si>
+  <si>
+    <t>PASTA  AL POMODORO  E CAPPERI</t>
+  </si>
+  <si>
     <t>MINESTRA DI PORRI</t>
   </si>
   <si>
     <t>ZUPPA DI CAROTE</t>
   </si>
   <si>
+    <t>ZUPPA DI PISELLI</t>
+  </si>
+  <si>
+    <t>ZUPPA DI PATATE</t>
+  </si>
+  <si>
+    <t>ROAST BEEF ALL'INGLESE</t>
+  </si>
+  <si>
+    <t>ARISTA DI MAIALE ALL' ALLORO</t>
+  </si>
+  <si>
+    <t>SCALOPPA DI MAIALE GRATINATA AGLI AROMI</t>
+  </si>
+  <si>
+    <t>ARISTA DI MAIALE AI  SEMI DI FINOCCHIO</t>
+  </si>
+  <si>
     <t>OMELETTE AL FORMAGGIO</t>
   </si>
   <si>
+    <t xml:space="preserve">SPEZZATINO  VEGANO CON FAVE SPEZIATO </t>
+  </si>
+  <si>
+    <t>HUMMUS DI CECI</t>
+  </si>
+  <si>
     <t>TORTA RUSTICA ALLE ZUCCHINE</t>
   </si>
   <si>
     <t>FILETTO DI MERLUZZO IN GUAZZETTO</t>
   </si>
   <si>
+    <t>FILETTO DI NASELLO IN UMIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILETTO DI PERSICO IN BAGNETTO </t>
+  </si>
+  <si>
     <t>ZUPPETTA DI PESCE IN COCCIO</t>
   </si>
   <si>
     <t>FAGIOLINI</t>
   </si>
   <si>
+    <t>PATATE AL FORNO</t>
+  </si>
+  <si>
     <t>GIOVEDÌ</t>
   </si>
   <si>
     <t>SPAGHETTI ALLA BOLOGNESE</t>
   </si>
   <si>
+    <t>PIZZOCCHERI</t>
+  </si>
+  <si>
+    <t>PASTA SPECK E FUNGHI</t>
+  </si>
+  <si>
+    <t>PASTA AL POMODORO E ORIGANO</t>
+  </si>
+  <si>
+    <t>PASTA AL POMODORO  E RICOTTA</t>
+  </si>
+  <si>
     <t>PASTA ALLA PIZZAIOLA</t>
   </si>
   <si>
+    <t>PASTA CON   POMODORO  E VERDURE</t>
+  </si>
+  <si>
+    <t>ZUPPA DI SEDANO</t>
+  </si>
+  <si>
+    <t>ZUPPA ALLA CONTADINA</t>
+  </si>
+  <si>
+    <t>PASSATA DI VERDURA</t>
+  </si>
+  <si>
     <t>INSALATA DI MARE</t>
   </si>
   <si>
+    <t>SFORMATO DI ZUCCA</t>
+  </si>
+  <si>
     <t>ROAST BEEF CON RUCOLA</t>
   </si>
   <si>
     <t>COTOLETTA DI TACCHINO</t>
   </si>
   <si>
+    <t>COCCIO DI BROCCOLI ,PORRI E SALSA DI SOYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACCHINO AL VAPORE CON ZENZERO FRESCO  </t>
+  </si>
+  <si>
+    <t>FILETTO DI SCORFANO AGLI AROMI</t>
+  </si>
+  <si>
+    <t>FESA DI TACCHINO ARROSTO</t>
+  </si>
+  <si>
+    <t>FETTUCCINE DI TOTANO CON PISELLI IN COCCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERZA,PATATE AGLIO E SALVIA IN COCCIO </t>
+  </si>
+  <si>
+    <t>CURRY DI VERDURE IN COCCIO</t>
+  </si>
+  <si>
     <t>CAROTE</t>
   </si>
   <si>
+    <t>FINOCCHI</t>
+  </si>
+  <si>
     <t>VENERDÌ</t>
   </si>
   <si>
+    <t>PASTA AL POMODORO E FUNGHI</t>
+  </si>
+  <si>
     <t>PASTA ALLA PUGLIESE</t>
   </si>
   <si>
     <t>SPAGHETTI  AGLIO OLIO E PEPERONCINO</t>
   </si>
   <si>
+    <t>SPAGHETTI  ALLA PORTOFINO</t>
+  </si>
+  <si>
     <t>PASTA ALLA PIEMONTESE</t>
   </si>
   <si>
+    <t>SPAGHETTI AL POMODORO  E BASILICO</t>
+  </si>
+  <si>
+    <t>SPAGHETTI CON  LE VERZE</t>
+  </si>
+  <si>
     <t>ZUPPA DI CAVOLO</t>
   </si>
   <si>
     <t>VELLUTATA DI VERDURA</t>
   </si>
   <si>
+    <t>MINESTRA DI FAGIOLI AZUKI</t>
+  </si>
+  <si>
     <t>LONZA AL FORNO</t>
   </si>
   <si>
+    <t>BRACIOLA DI MAIALE IN SALSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACCHINO FUME' CON RUCOLA </t>
+  </si>
+  <si>
     <t>FILETTO DI NASELLO GRATINATO</t>
   </si>
   <si>
+    <t>FILETTO DI SCORFANO</t>
+  </si>
+  <si>
     <t>FILETTO DI NASELLO PREZZEMOLATO</t>
   </si>
   <si>
+    <t>,COCCIO DI VERDURE GRIGLIATE E PROVOLA FUME’</t>
+  </si>
+  <si>
     <t>INSALATONA</t>
   </si>
   <si>
     <t>BURGHER DI BROCCOLI</t>
   </si>
   <si>
+    <t>SCALOPPINA ALLA SALVIA</t>
+  </si>
+  <si>
     <t>PATATE PREZZEMOLATE</t>
   </si>
   <si>
+    <t>SPINACI</t>
+  </si>
+  <si>
     <t>PATATE AL VAPORE</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <rFont val="Comic Sans MS"/>
+        <family val="4"/>
+      </rPr>
+      <t xml:space="preserve">MENU INVERNO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="8"/>
+        <rFont val="Comic Sans MS"/>
+        <family val="4"/>
+      </rPr>
+      <t>LEONARDO 202</t>
+    </r>
+  </si>
+  <si>
+    <t>PASTA SG PESTO</t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA CARRETTIERA</t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA TRAPANESE</t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA PUTTANESCA</t>
+  </si>
+  <si>
+    <t>RISO IN BIANCO</t>
+  </si>
+  <si>
+    <t>PROSCIUTTO COTTO O SALAME</t>
+  </si>
+  <si>
+    <t>FORMAGGIO CONFEZIONATO</t>
+  </si>
+  <si>
+    <t>PASTA SG ALL' AMATRICIANA</t>
+  </si>
+  <si>
+    <t>PASTA SG AI CARCIOFI</t>
+  </si>
+  <si>
+    <t>RISOTTO  AL RADICCHIO E VINO ROSSO</t>
+  </si>
+  <si>
+    <t>INSALATA DI TONNO, OLIVE E FAGIOLINI</t>
+  </si>
+  <si>
+    <t>FRITTATA CON VERDURE</t>
+  </si>
+  <si>
+    <t>BRESAOLA</t>
+  </si>
+  <si>
+    <t>ZUCCHINE</t>
+  </si>
+  <si>
+    <t>FAGIOLI</t>
+  </si>
+  <si>
+    <t>ZUCCHINE AL VAPORE</t>
+  </si>
+  <si>
     <t>PASTA ALL’ ARRABBIATA</t>
   </si>
   <si>
+    <t>PASTA  ALLA ZUCCA E SALSICCIA</t>
+  </si>
+  <si>
+    <t>FILETTO DI PERSICO IN BAGNETTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAGIOLI </t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA BOLOGNESE</t>
+  </si>
+  <si>
+    <t>PASTA SG AL POMODORO  E RICOTTA</t>
+  </si>
+  <si>
+    <t>PASTA SG CON POMODORO E VERDURE</t>
+  </si>
+  <si>
+    <t>TACCHINO AL VAPORE CON ZENZERO FRESCO</t>
+  </si>
+  <si>
+    <t>PROSCIUTTO COTTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZUCCHINE </t>
+  </si>
+  <si>
+    <t>PASTA SG AL POMODORO E FUNGHI</t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA PUGLIESE</t>
+  </si>
+  <si>
+    <t>PASTA SG AL POMODORO  E BASILICO</t>
+  </si>
+  <si>
+    <t>PASTA SG CON  LE VERZE</t>
+  </si>
+  <si>
+    <t>MENU LEONARDO CASCINA COSTA  2025/26 – INVERNO    DAL 12/01/26 prima settimana</t>
+  </si>
+  <si>
+    <t>OMELETTE AGLI SPINACI</t>
+  </si>
+  <si>
+    <t>PROSCIUTTO CRUDO</t>
+  </si>
+  <si>
+    <t>PASTA SG ALLA PIZZAIOLA</t>
+  </si>
+  <si>
+    <t>ARISTA DI MAIALE CON PISELLI</t>
+  </si>
+  <si>
+    <t>BIETA</t>
+  </si>
+  <si>
+    <t>BURGHER DI CECI, CAROTE E POMODORO SECCO</t>
+  </si>
+  <si>
     <t>PASTA AI  BROCCOLI</t>
+  </si>
+  <si>
+    <t>OMELETTE CON SPINACI</t>
+  </si>
+  <si>
+    <t>LASAGNE AL RAGU'</t>
   </si>
   <si>
     <r>
@@ -220,252 +578,14 @@
     </r>
   </si>
   <si>
-    <t>INSALATA DI TONNO E FAGIOLI</t>
-  </si>
-  <si>
-    <t>COSCIA DI POLLO ALLA DIAVOLA</t>
-  </si>
-  <si>
-    <t>CAROTE AL VAPORE</t>
-  </si>
-  <si>
-    <t>RISOTTO ALLA CRESCENZA E ZUCCHINE</t>
-  </si>
-  <si>
-    <t>CREMA DI PORRI</t>
-  </si>
-  <si>
-    <t>VITELLONE BOLLITO CON SALSA VERDE</t>
-  </si>
-  <si>
-    <t>PASTA ALL'AMATRICIANA</t>
-  </si>
-  <si>
-    <t>PASTA AI 4 FORMAGGI</t>
-  </si>
-  <si>
-    <t>MINESTRA ALLA CONTADINA</t>
-  </si>
-  <si>
-    <t>LONZA ALL’ALLORO</t>
-  </si>
-  <si>
-    <t>COCCIO AI BROCCOLI   E.V.O.  E OLIVE
-VEGANO</t>
-  </si>
-  <si>
-    <t>PATATE ARROSTO</t>
-  </si>
-  <si>
-    <t>LINGUINE ALLO SCOGLIO</t>
-  </si>
-  <si>
-    <t>LINGUINE AGLIO E OLIO E PROFUMO DI 
-AGRUMI</t>
-  </si>
-  <si>
-    <t>FRITTATA CON FRIARIELLI</t>
-  </si>
-  <si>
-    <t>FESA DI TACCHINO ARROSTO CON MIREPOIX</t>
-  </si>
-  <si>
-    <t>PASTA AL GAZPACHO</t>
-  </si>
-  <si>
-    <t>ZUPPA DI FAGIOLI ROSSI AZUKI</t>
-  </si>
-  <si>
-    <t>ARISTA DI MAIALE AL POMODORO E ORIGANO</t>
-  </si>
-  <si>
-    <t>BURGHER DI ZUCCA E CAROTE</t>
-  </si>
-  <si>
-    <t>MISTO CEREALI CON VERDURE E
-QUARTIROLO</t>
-  </si>
-  <si>
-    <t>MINESTRA DI CECI</t>
-  </si>
-  <si>
-    <t>BOCCONCINI DI TACCHINO CON PISELLI</t>
-  </si>
-  <si>
-    <t>GNOCCHI AL POMODORO E BASILICO</t>
-  </si>
-  <si>
-    <t>KEBAB</t>
-  </si>
-  <si>
-    <t>FRITTATA ALL'ORTOLANA</t>
-  </si>
-  <si>
-    <t>FILETTO DI PERSICO ALLA GRENOBLESE</t>
-  </si>
-  <si>
-    <t>RISO PILAF CURCUMA E VERDURE</t>
-  </si>
-  <si>
-    <t>PASTA AL TONNO E CAPPERI</t>
-  </si>
-  <si>
-    <t>MINESTRA DI SEDANO</t>
-  </si>
-  <si>
-    <t>SPEZZATINO VEGANO CON FAVE SPEZIATO
-AL GINGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINOCCHI   </t>
-  </si>
-  <si>
-    <t>SPAGHETTI AL POMODORO E RICOTTA</t>
-  </si>
-  <si>
-    <t>SFORMATO AI BROCCOLI</t>
-  </si>
-  <si>
-    <t>FETTUCCE DI TOTANO CON PISELLI</t>
-  </si>
-  <si>
-    <t>INSALATA DI POLLO</t>
-  </si>
-  <si>
-    <t>PASTA ALLA FONDUTA DI CURCUMA E PEPE</t>
-  </si>
-  <si>
-    <t>BRACIOLA DI MAIALE AL VINO BIANCO</t>
-  </si>
-  <si>
-    <t>FILETTO DI MERLUZZO AL LIMONE</t>
-  </si>
-  <si>
-    <t>INSALATA DI  TONNO,FAGIOLINI, PATATE E
-OLIVE</t>
-  </si>
-  <si>
-    <t>PASTA AL POMODORO E RUCOLA</t>
-  </si>
-  <si>
-    <t>ARISTA ARROSTO AI FUNGHI</t>
-  </si>
-  <si>
-    <t>FILETTO DI MERLUZZO AL SALMORIGLIO</t>
-  </si>
-  <si>
-    <t>TORTINO ARRAGANATO</t>
-  </si>
-  <si>
-    <t>PASTA CON LE MELANZANE</t>
-  </si>
-  <si>
-    <t>PASTA AL SUGO FINTO</t>
-  </si>
-  <si>
-    <t>SCALOPPA DI MAIALE GRATINATA</t>
-  </si>
-  <si>
-    <t>HUMMUS DI CECI CON CROSTONE</t>
-  </si>
-  <si>
-    <t>FILETTO DI SCORFANO CON ZUCCHINE 
-MARINATE</t>
-  </si>
-  <si>
-    <t>PASTA SPECK E PISELLI</t>
-  </si>
-  <si>
-    <t>PASTA  ALL' ORTOLANA</t>
-  </si>
-  <si>
-    <t>FESA DI TACCHINO AL MARSALA</t>
-  </si>
-  <si>
-    <t>PROVOLONE AL FORNO CON POMODORO</t>
-  </si>
-  <si>
-    <t>SPAGHETTI AL POMODORO E ACCIUGA</t>
-  </si>
-  <si>
-    <t>PASSATA DI LEGUMI</t>
-  </si>
-  <si>
-    <t>INSALATA DI FARRO E VERDURE</t>
-  </si>
-  <si>
-    <t>FILETTO DI MERLUZZO IMPANATO</t>
-  </si>
-  <si>
-    <t>FILETTO DI PERSICO AL SALMORIGLIO</t>
-  </si>
-  <si>
-    <t>INSALATA DI RISO</t>
-  </si>
-  <si>
-    <t>PASTA AL POMODORO E CAPPERI</t>
-  </si>
-  <si>
-    <t>ZUPPA PRIMAVERA</t>
-  </si>
-  <si>
-    <t>ROAST -BEEF CALL'INGLESE</t>
-  </si>
-  <si>
-    <t>GNOCCHI AL RAGU’</t>
-  </si>
-  <si>
-    <t>MINESTRA DI PATATE</t>
-  </si>
-  <si>
-    <t>CURRY DI VERDURE</t>
-  </si>
-  <si>
-    <t>CAVOLINI DI BRUXELLES</t>
-  </si>
-  <si>
-    <t>SPAGHETTI  AL POMODORO E FUNGHI</t>
-  </si>
-  <si>
-    <t>SPAGHETTI AL PESTATO DI CAVOLO</t>
-  </si>
-  <si>
-    <t>PASSATA DI VERDURE</t>
-  </si>
-  <si>
-    <t>TACCHINO FUME' CON RUCOLA</t>
-  </si>
-  <si>
-    <t>SCALOPPINA DI MAIALE ALLA SALVIA</t>
-  </si>
-  <si>
-    <t>BIETE</t>
-  </si>
-  <si>
-    <t>LEGUMI(STUFATI SE FA FREDDO
-PREZZEMOLATI SE FA CALDO)</t>
-  </si>
-  <si>
-    <t>MENU LEONARDO CASCINA COSTA  - PRIMAVERA    DAL 30/03/26 prima settimana</t>
-  </si>
-  <si>
-    <t>PASTA AL POMODORO ,PATATE E_x000D_
-ROSMARINO</t>
-  </si>
-  <si>
-    <t>ARISTA ALLA FIORENTINA (SEMI DI _x000D_
-FINOCCHIO)</t>
-  </si>
-  <si>
-    <t>COCCIO DI PATATE GRATINATE ALLA CREMA
-DI LATTE E NOCE MOSCATA</t>
+    <t>MENU LEONARDO CASCINA COSTA  - INVERNO    DAL 7/01/26 prima settimana</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -524,6 +644,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -557,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -682,16 +815,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="8"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="8"/>
       </bottom>
       <diagonal/>
@@ -700,10 +831,10 @@
       <left style="medium">
         <color indexed="8"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="8"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
@@ -715,13 +846,13 @@
       <left style="medium">
         <color indexed="8"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="8"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="8"/>
       </bottom>
       <diagonal/>
@@ -730,10 +861,107 @@
       <left style="medium">
         <color indexed="8"/>
       </left>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color indexed="8"/>
       </top>
       <bottom style="medium">
@@ -745,7 +973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -798,25 +1026,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -825,23 +1077,41 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -877,13 +1147,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1033" name="Immagine 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1033" name="Immagine 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -905,6 +1169,175 @@
         <a:xfrm>
           <a:off x="15900400" y="0"/>
           <a:ext cx="2165350" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:blipFill dpi="0" rotWithShape="0">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+                <a:srcRect/>
+                <a:stretch>
+                  <a:fillRect/>
+                </a:stretch>
+              </a:blipFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3465A4"/>
+              </a:solidFill>
+              <a:round/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>882650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3067050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2061" name="Immagine 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15119350" y="19050"/>
+          <a:ext cx="2184400" cy="412750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:blipFill dpi="0" rotWithShape="0">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+                <a:srcRect/>
+                <a:stretch>
+                  <a:fillRect/>
+                </a:stretch>
+              </a:blipFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="3465A4"/>
+              </a:solidFill>
+              <a:round/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>882650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3073400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2062" name="Immagine 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15119350" y="19050"/>
+          <a:ext cx="2190750" cy="412750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1307,28 +1740,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.28515625" style="1" customWidth="1"/>
-    <col min="3" max="6" width="50.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="2"/>
-    <col min="8" max="8" width="50.7109375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="2" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="50.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" style="2"/>
+    <col min="8" max="8" width="50.7265625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1336,12 +1769,12 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="26"/>
+    <row r="3" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="34"/>
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1355,11 +1788,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1367,572 +1800,572 @@
         <v>6</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="12" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="D19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="25" spans="1:7" s="14" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="D25" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="E25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" spans="1:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E30" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D31" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="E31" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="12" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="F31" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" spans="1:7" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="D32" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" spans="1:6" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="B33" s="28"/>
+      <c r="C33" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="14" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="15"/>
-    </row>
-    <row r="27" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="E33" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" s="8" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="1:7" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F34" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="9" t="s">
+    <row r="39" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="26" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="11" t="s">
+      <c r="D39" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="9" t="s">
+      <c r="F39" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -1959,4 +2392,622 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="61.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="61.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" style="2"/>
+    <col min="8" max="8" width="50.7265625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="45"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="12" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="14" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="46"/>
+      <c r="C23" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="1:7" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" spans="1:7" ht="30.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="41"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+    <row r="37" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="C37" s="23"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" ht="21.5" x14ac:dyDescent="0.25">
+      <c r="D38" s="24"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" ht="21.5" x14ac:dyDescent="0.25">
+      <c r="D39" s="24"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" ht="21.5" x14ac:dyDescent="0.25">
+      <c r="D40" s="24"/>
+      <c r="F40" s="24"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A30:B35"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B10"/>
+    <mergeCell ref="A11:B16"/>
+    <mergeCell ref="A17:B22"/>
+    <mergeCell ref="A23:B29"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="49" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;C&amp;1#&amp;"Calibri"&amp;10&amp;K000000Company General Use</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="6" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>